--- a/july 2026/LMT_JULY_26/Umaima Paragon city.xlsx
+++ b/july 2026/LMT_JULY_26/Umaima Paragon city.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9701F32-FBC2-45C6-A917-9684D96D1FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3805BA-C0FC-4F55-9271-4A780D8D3899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3385,7 +3385,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3413,7 +3413,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4628,7 +4628,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4656,7 +4656,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5871,7 +5871,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5899,7 +5899,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7114,7 +7114,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7142,7 +7142,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8357,7 +8357,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8385,7 +8385,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9600,7 +9600,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9628,7 +9628,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10843,7 +10843,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10871,7 +10871,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12086,7 +12086,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12114,7 +12114,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13329,7 +13329,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13357,7 +13357,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14572,7 +14572,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14600,7 +14600,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18565,7 +18565,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18593,7 +18593,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19805,7 +19805,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19833,7 +19833,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21044,7 +21044,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21072,7 +21072,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22283,7 +22283,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22311,7 +22311,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23527,7 +23527,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23555,7 +23555,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25072,7 +25072,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25100,7 +25100,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -26206,7 +26206,7 @@
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N33:O33"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
@@ -26221,7 +26221,7 @@
   <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000003000000}">
           <x14:formula1>
             <xm:f>Sheet2!$B$6:$B$13</xm:f>
@@ -26310,7 +26310,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26338,7 +26338,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27553,7 +27553,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27581,7 +27581,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28795,7 +28795,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28823,7 +28823,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30038,7 +30038,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30066,7 +30066,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31282,7 +31282,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31310,7 +31310,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
